--- a/sources/king_step6b.xlsx
+++ b/sources/king_step6b.xlsx
@@ -6890,7 +6890,7 @@
       </c>
       <c r="K128" t="inlineStr">
         <is>
-          <t>[!]</t>
+          <t>!</t>
         </is>
       </c>
       <c r="O128" t="inlineStr">

--- a/sources/king_step6b.xlsx
+++ b/sources/king_step6b.xlsx
@@ -1129,6 +1129,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
+        </is>
+      </c>
       <c r="R14" t="inlineStr">
         <is>
           <t>67ff2023-6e37-4766-ab77-10e230c708b4</t>
@@ -1171,6 +1176,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
+        </is>
+      </c>
       <c r="R15" t="inlineStr">
         <is>
           <t>c4c3cd71-ed27-44df-a655-fb09f78b6be8</t>
@@ -1213,6 +1223,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>f8794d93-a444-4657-859f-d2548700e248</t>
+        </is>
+      </c>
       <c r="R16" t="inlineStr">
         <is>
           <t>f8794d93-a444-4657-859f-d2548700e248</t>
@@ -1255,6 +1270,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
+        </is>
+      </c>
       <c r="R17" t="inlineStr">
         <is>
           <t>9821af5c-9a74-43da-8d33-7092f2b7ff7b</t>
@@ -1307,6 +1327,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
+        </is>
+      </c>
       <c r="R18" t="inlineStr">
         <is>
           <t>7df0cfa5-026b-4ff9-9f39-55c477962d0f</t>
@@ -1344,6 +1369,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
+        </is>
+      </c>
       <c r="R19" t="inlineStr">
         <is>
           <t>f8490fa0-7b1f-4f39-99ab-da6ae361ed20</t>
@@ -1386,6 +1416,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
+        </is>
+      </c>
       <c r="R20" t="inlineStr">
         <is>
           <t>68f074ca-3602-4223-bca2-a6b2ec87ef2a</t>
@@ -1428,6 +1463,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
+        </is>
+      </c>
       <c r="R21" t="inlineStr">
         <is>
           <t>0176585b-588a-49e1-9572-4bdd7101f82a</t>
@@ -1470,6 +1510,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
+        </is>
+      </c>
       <c r="R22" t="inlineStr">
         <is>
           <t>00ddf7e7-6010-4a77-9ae6-40ef2f2a707a</t>
@@ -1512,6 +1557,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
+        </is>
+      </c>
       <c r="R23" t="inlineStr">
         <is>
           <t>b6c23f31-cb1a-450f-9a17-e7cc5b124033</t>
@@ -1554,6 +1604,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q24" t="inlineStr">
+        <is>
+          <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
+        </is>
+      </c>
       <c r="R24" t="inlineStr">
         <is>
           <t>12308a0d-a04e-49ad-a92e-7b32fb03c49f</t>
@@ -1596,6 +1651,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q25" t="inlineStr">
+        <is>
+          <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
+        </is>
+      </c>
       <c r="R25" t="inlineStr">
         <is>
           <t>6c0cc2bf-f0ad-4b46-a1ff-2a7de8bdb37f</t>
@@ -1638,6 +1698,11 @@
           <t>System</t>
         </is>
       </c>
+      <c r="Q26" t="inlineStr">
+        <is>
+          <t>377bd68e-1783-43e2-8c72-05143260300a</t>
+        </is>
+      </c>
       <c r="R26" t="inlineStr">
         <is>
           <t>377bd68e-1783-43e2-8c72-05143260300a</t>
@@ -1680,6 +1745,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
+        </is>
+      </c>
       <c r="R27" t="inlineStr">
         <is>
           <t>f57394c8-7aba-414b-af3e-d37941cae2e3</t>
@@ -1732,6 +1802,11 @@
           <t>The Counter Hit Stomach Smash is NOT a throw but is required before you can do the 2 throw follow ups.</t>
         </is>
       </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
+        </is>
+      </c>
       <c r="R28" t="inlineStr">
         <is>
           <t>b2d4546c-7d86-4fee-a8f7-dbe4e5857d92</t>
@@ -1769,6 +1844,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
+        </is>
+      </c>
       <c r="R29" t="inlineStr">
         <is>
           <t>829ce921-0e10-4ab2-bbbc-911f844eceef</t>
@@ -1811,6 +1891,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
+        </is>
+      </c>
       <c r="R30" t="inlineStr">
         <is>
           <t>db0aa370-9079-45e2-b39c-7472d8bae8a4</t>
@@ -1863,6 +1948,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
+        </is>
+      </c>
       <c r="R31" t="inlineStr">
         <is>
           <t>6294b53d-e480-4df4-be9f-98a25b5e6a95</t>
@@ -1910,6 +2000,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q32" t="inlineStr">
+        <is>
+          <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
+        </is>
+      </c>
       <c r="R32" t="inlineStr">
         <is>
           <t>16314dd7-17de-43e3-89e8-146678a228d1</t>
@@ -1957,6 +2052,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
+        </is>
+      </c>
       <c r="R33" t="inlineStr">
         <is>
           <t>ab65c71e-57c4-4826-b7e0-038c4501bdc6</t>
@@ -1999,6 +2099,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
+        </is>
+      </c>
       <c r="R34" t="inlineStr">
         <is>
           <t>fe0b77cb-f2dd-4ba4-b684-d4ecf9d4a053</t>
@@ -2039,6 +2144,11 @@
       <c r="M35" t="inlineStr">
         <is>
           <t>None</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>a7a77dd9-2c48-4420-8555-24aab9d0520c</t>
         </is>
       </c>
       <c r="R35" t="inlineStr">
@@ -2198,6 +2308,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
+        </is>
+      </c>
       <c r="R39" t="inlineStr">
         <is>
           <t>014ddb56-1613-49f0-9e34-a5e1f6c785fe</t>
@@ -2245,6 +2360,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
+        </is>
+      </c>
       <c r="R40" t="inlineStr">
         <is>
           <t>8b30b6c0-0bc1-4441-8820-964886587202</t>
@@ -2287,6 +2407,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>1a628a44-4c66-4d94-b410-673005311f11</t>
+        </is>
+      </c>
       <c r="R41" t="inlineStr">
         <is>
           <t>1a628a44-4c66-4d94-b410-673005311f11</t>
@@ -2329,6 +2454,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
+        </is>
+      </c>
       <c r="R42" t="inlineStr">
         <is>
           <t>912252eb-66d4-4874-abc8-0c9951b57b07</t>
@@ -2371,6 +2501,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>78755529-5600-440c-8380-ad656059ff13</t>
+        </is>
+      </c>
       <c r="R43" t="inlineStr">
         <is>
           <t>78755529-5600-440c-8380-ad656059ff13</t>
@@ -2418,6 +2553,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
+        </is>
+      </c>
       <c r="R44" t="inlineStr">
         <is>
           <t>3d784cd2-6e86-46a8-bbd0-6f0b4d5c473c</t>
@@ -2465,6 +2605,11 @@
           <t>3+4</t>
         </is>
       </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
+        </is>
+      </c>
       <c r="R45" t="inlineStr">
         <is>
           <t>97fdc64c-6825-4fbc-b64c-406c522a9288</t>
@@ -2512,6 +2657,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
+        </is>
+      </c>
       <c r="R46" t="inlineStr">
         <is>
           <t>4b9555c8-11ce-4fb0-af28-67c8956588ae</t>
@@ -2559,6 +2709,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
+        </is>
+      </c>
       <c r="R47" t="inlineStr">
         <is>
           <t>cb6d3d00-45b4-40eb-8e80-dff09bade591</t>
@@ -2604,6 +2759,11 @@
       <c r="M48" t="inlineStr">
         <is>
           <t>1</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>44cede5f-e666-42c2-b9ea-20ca0d73478e</t>
         </is>
       </c>
       <c r="R48" t="inlineStr">
@@ -7050,6 +7210,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q132" t="inlineStr">
+        <is>
+          <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
+        </is>
+      </c>
       <c r="R132" t="inlineStr">
         <is>
           <t>d14fb2bb-b9cb-4ac9-9db3-e052c90daa2f</t>
@@ -7087,6 +7252,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q133" t="inlineStr">
+        <is>
+          <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
+        </is>
+      </c>
       <c r="R133" t="inlineStr">
         <is>
           <t>754287bc-eb16-4fb1-adf5-9ba198ef61bc</t>
@@ -7129,6 +7299,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q134" t="inlineStr">
+        <is>
+          <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
+        </is>
+      </c>
       <c r="R134" t="inlineStr">
         <is>
           <t>610d1988-6af6-4bcc-a947-eb4020bc3119</t>
@@ -7171,6 +7346,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Q135" t="inlineStr">
+        <is>
+          <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
+        </is>
+      </c>
       <c r="R135" t="inlineStr">
         <is>
           <t>ffa2eb74-b7c8-48f6-b268-2882ba61fae0</t>
@@ -7213,6 +7393,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q136" t="inlineStr">
+        <is>
+          <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
+        </is>
+      </c>
       <c r="R136" t="inlineStr">
         <is>
           <t>318177e8-8c06-4cfe-a628-4c3f588e36e9</t>
@@ -7265,6 +7450,11 @@
           <t>After the initial grab use 3+4 to escape.</t>
         </is>
       </c>
+      <c r="Q137" t="inlineStr">
+        <is>
+          <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
+        </is>
+      </c>
       <c r="R137" t="inlineStr">
         <is>
           <t>e9174a35-b2b1-40d7-8704-552434c99980</t>
@@ -7307,6 +7497,11 @@
           <t>Double Arm Face Buster is not additional damage to the Jaguar Driver, it add 5 points of damage.</t>
         </is>
       </c>
+      <c r="Q138" t="inlineStr">
+        <is>
+          <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
+        </is>
+      </c>
       <c r="R138" t="inlineStr">
         <is>
           <t>61fbd176-0a6e-4368-89b2-fae51c957338</t>
@@ -7349,6 +7544,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q139" t="inlineStr">
+        <is>
+          <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
+        </is>
+      </c>
       <c r="R139" t="inlineStr">
         <is>
           <t>e370e475-82e9-42c2-9dda-e815185d01ba</t>
@@ -7396,6 +7596,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q140" t="inlineStr">
+        <is>
+          <t>d0dc416c-d281-41de-a830-391175b9c733</t>
+        </is>
+      </c>
       <c r="R140" t="inlineStr">
         <is>
           <t>d0dc416c-d281-41de-a830-391175b9c733</t>
@@ -7433,6 +7638,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Q141" t="inlineStr">
+        <is>
+          <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
+        </is>
+      </c>
       <c r="R141" t="inlineStr">
         <is>
           <t>c1efc095-a281-425f-89ef-e6a21a09748e</t>
@@ -7475,6 +7685,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q142" t="inlineStr">
+        <is>
+          <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
+        </is>
+      </c>
       <c r="R142" t="inlineStr">
         <is>
           <t>ca3bdbfd-726c-4c6a-8a68-16d368d953de</t>
@@ -7517,6 +7732,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q143" t="inlineStr">
+        <is>
+          <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
+        </is>
+      </c>
       <c r="R143" t="inlineStr">
         <is>
           <t>576fbd03-9817-4433-aee9-a05fb2873ee9</t>
@@ -7559,6 +7779,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q144" t="inlineStr">
+        <is>
+          <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
+        </is>
+      </c>
       <c r="R144" t="inlineStr">
         <is>
           <t>bf90b650-01f4-4fc9-88b8-319864f95c86</t>
@@ -7601,6 +7826,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q145" t="inlineStr">
+        <is>
+          <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
+        </is>
+      </c>
       <c r="R145" t="inlineStr">
         <is>
           <t>9cb56a53-599f-4719-9b84-f7e40bb6afa8</t>
@@ -7643,6 +7873,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q146" t="inlineStr">
+        <is>
+          <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
+        </is>
+      </c>
       <c r="R146" t="inlineStr">
         <is>
           <t>c053f961-d2f8-4fbd-83ae-34fca200b9b7</t>
@@ -7700,6 +7935,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="Q147" t="inlineStr">
+        <is>
+          <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
+        </is>
+      </c>
       <c r="R147" t="inlineStr">
         <is>
           <t>8a657c3c-5962-4744-8afb-8db34e185b60</t>
@@ -7742,6 +7982,11 @@
           <t>Escape with 1 if the multi was started with 1+3 and 2 if the multi was started with 2+4.</t>
         </is>
       </c>
+      <c r="Q148" t="inlineStr">
+        <is>
+          <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
+        </is>
+      </c>
       <c r="R148" t="inlineStr">
         <is>
           <t>e9b59331-5359-43c8-a2fe-c2f1c768010e</t>
@@ -7784,6 +8029,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q149" t="inlineStr">
+        <is>
+          <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
+        </is>
+      </c>
       <c r="R149" t="inlineStr">
         <is>
           <t>a35b6adb-c2ae-4dcc-8c1c-e89ddf41df28</t>
@@ -7826,6 +8076,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q150" t="inlineStr">
+        <is>
+          <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
+        </is>
+      </c>
       <c r="R150" t="inlineStr">
         <is>
           <t>a076bd88-cfd9-4b82-b29b-751f8994df70</t>
@@ -7868,6 +8123,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q151" t="inlineStr">
+        <is>
+          <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
+        </is>
+      </c>
       <c r="R151" t="inlineStr">
         <is>
           <t>897562ea-11c8-48e1-bdd7-3508028d9455</t>
@@ -7910,6 +8170,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q152" t="inlineStr">
+        <is>
+          <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
+        </is>
+      </c>
       <c r="R152" t="inlineStr">
         <is>
           <t>0499e709-28d1-44ad-884c-143bf75b7436</t>
@@ -7952,6 +8217,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q153" t="inlineStr">
+        <is>
+          <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
+        </is>
+      </c>
       <c r="R153" t="inlineStr">
         <is>
           <t>988107cd-c43e-41b1-bec3-f6450eebd275</t>
@@ -7994,6 +8264,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q154" t="inlineStr">
+        <is>
+          <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
+        </is>
+      </c>
       <c r="R154" t="inlineStr">
         <is>
           <t>54aa2be5-501e-441f-b759-e6eaa8b2c7aa</t>
@@ -8036,6 +8311,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q155" t="inlineStr">
+        <is>
+          <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
+        </is>
+      </c>
       <c r="R155" t="inlineStr">
         <is>
           <t>e36e2276-3cc6-43b4-bef5-0d88f962c067</t>
@@ -8078,6 +8358,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q156" t="inlineStr">
+        <is>
+          <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
+        </is>
+      </c>
       <c r="R156" t="inlineStr">
         <is>
           <t>91806b57-15f2-453a-9e66-6e9265eb3f74</t>
@@ -8120,6 +8405,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q157" t="inlineStr">
+        <is>
+          <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
+        </is>
+      </c>
       <c r="R157" t="inlineStr">
         <is>
           <t>0d22dd12-3fab-495f-bd30-0dd66be69ec9</t>
@@ -8162,6 +8452,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q158" t="inlineStr">
+        <is>
+          <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
+        </is>
+      </c>
       <c r="R158" t="inlineStr">
         <is>
           <t>0b34d2a0-d07c-4603-9984-9e48ffa8b289</t>
@@ -8204,6 +8499,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q159" t="inlineStr">
+        <is>
+          <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
+        </is>
+      </c>
       <c r="R159" t="inlineStr">
         <is>
           <t>3a88bc91-07bf-4196-bbfc-65d00fdc5cdb</t>
@@ -8246,6 +8546,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q160" t="inlineStr">
+        <is>
+          <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
+        </is>
+      </c>
       <c r="R160" t="inlineStr">
         <is>
           <t>88d1f06b-09b4-4f3b-b26f-6b7eb09839b9</t>
@@ -8293,6 +8598,11 @@
           <t>1+2</t>
         </is>
       </c>
+      <c r="Q161" t="inlineStr">
+        <is>
+          <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
+        </is>
+      </c>
       <c r="R161" t="inlineStr">
         <is>
           <t>21a93725-b013-4fd7-b6a0-53b29c951345</t>
@@ -8340,6 +8650,11 @@
           <t>If grabbed from the side or back then Cannonball will be the 1st part of the Multi Throw.</t>
         </is>
       </c>
+      <c r="Q162" t="inlineStr">
+        <is>
+          <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
+        </is>
+      </c>
       <c r="R162" t="inlineStr">
         <is>
           <t>e5cfb3e7-d8eb-43a9-95a5-78b47376b89c</t>
@@ -8382,6 +8697,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q163" t="inlineStr">
+        <is>
+          <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
+        </is>
+      </c>
       <c r="R163" t="inlineStr">
         <is>
           <t>d29031f4-9c39-4518-8ca7-d1d579f731d3</t>
@@ -8419,6 +8739,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q164" t="inlineStr">
+        <is>
+          <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
+        </is>
+      </c>
       <c r="R164" t="inlineStr">
         <is>
           <t>cf747642-f5e0-4884-9c87-bf258ea86c4c</t>
@@ -8461,6 +8786,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q165" t="inlineStr">
+        <is>
+          <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
+        </is>
+      </c>
       <c r="R165" t="inlineStr">
         <is>
           <t>90ec3fb9-f4d7-421a-99e2-e37e4a49ce00</t>
@@ -8503,6 +8833,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q166" t="inlineStr">
+        <is>
+          <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
+        </is>
+      </c>
       <c r="R166" t="inlineStr">
         <is>
           <t>334b113e-5fa6-4350-8c7f-d1443e15e6b7</t>
@@ -8545,6 +8880,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q167" t="inlineStr">
+        <is>
+          <t>58f13036-58ee-4611-a14d-d783777422a0</t>
+        </is>
+      </c>
       <c r="R167" t="inlineStr">
         <is>
           <t>58f13036-58ee-4611-a14d-d783777422a0</t>
@@ -8587,6 +8927,11 @@
           <t>2</t>
         </is>
       </c>
+      <c r="Q168" t="inlineStr">
+        <is>
+          <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
+        </is>
+      </c>
       <c r="R168" t="inlineStr">
         <is>
           <t>f7973f34-41fe-4bf5-95c3-8fb79ee2452d</t>
@@ -8629,6 +8974,11 @@
           <t>None</t>
         </is>
       </c>
+      <c r="Q169" t="inlineStr">
+        <is>
+          <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
+        </is>
+      </c>
       <c r="R169" t="inlineStr">
         <is>
           <t>0515905e-bcfb-496f-bbfc-01dedb07caa4</t>
@@ -8671,6 +9021,11 @@
           <t>1</t>
         </is>
       </c>
+      <c r="Q170" t="inlineStr">
+        <is>
+          <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
+        </is>
+      </c>
       <c r="R170" t="inlineStr">
         <is>
           <t>fefe8385-3ffe-4743-8071-1a48c86080c5</t>
@@ -8711,6 +9066,11 @@
       <c r="M171" t="inlineStr">
         <is>
           <t>2</t>
+        </is>
+      </c>
+      <c r="Q171" t="inlineStr">
+        <is>
+          <t>cd229188-1f00-4e2c-beb7-0ecdab35b8dc</t>
         </is>
       </c>
       <c r="R171" t="inlineStr">
@@ -8860,6 +9220,11 @@
           <t>hhmmhLLLmM</t>
         </is>
       </c>
+      <c r="Q175" t="inlineStr">
+        <is>
+          <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
+        </is>
+      </c>
       <c r="R175" t="inlineStr">
         <is>
           <t>540396d1-00a1-4033-9fce-7dbbcf91bebf</t>
@@ -8892,6 +9257,11 @@
           <t>hhmmhLLLmh</t>
         </is>
       </c>
+      <c r="Q176" t="inlineStr">
+        <is>
+          <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
+        </is>
+      </c>
       <c r="R176" t="inlineStr">
         <is>
           <t>53b541e0-d1fa-4602-8e8e-198dc6d57441</t>
@@ -8924,6 +9294,11 @@
           <t>hhmmhmLLmM</t>
         </is>
       </c>
+      <c r="Q177" t="inlineStr">
+        <is>
+          <t>d76e55af-5e37-469f-b459-858d5c452608</t>
+        </is>
+      </c>
       <c r="R177" t="inlineStr">
         <is>
           <t>d76e55af-5e37-469f-b459-858d5c452608</t>
@@ -8956,6 +9331,11 @@
           <t>hhmmhmLLmh</t>
         </is>
       </c>
+      <c r="Q178" t="inlineStr">
+        <is>
+          <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
+        </is>
+      </c>
       <c r="R178" t="inlineStr">
         <is>
           <t>10ceada9-d82e-41bd-b56c-5a3fa1400921</t>
@@ -8988,6 +9368,11 @@
           <t>hhmmhmLLlthrow</t>
         </is>
       </c>
+      <c r="Q179" t="inlineStr">
+        <is>
+          <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
+        </is>
+      </c>
       <c r="R179" t="inlineStr">
         <is>
           <t>5c5c8a42-acd0-4b4b-88f6-39a67110202e</t>
@@ -9020,6 +9405,11 @@
           <t>hmmhLLLmM</t>
         </is>
       </c>
+      <c r="Q180" t="inlineStr">
+        <is>
+          <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
+        </is>
+      </c>
       <c r="R180" t="inlineStr">
         <is>
           <t>47c1d8e6-c95b-4542-b264-13a374b2c050</t>
@@ -9052,6 +9442,11 @@
           <t>hmmhLLLmh</t>
         </is>
       </c>
+      <c r="Q181" t="inlineStr">
+        <is>
+          <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
+        </is>
+      </c>
       <c r="R181" t="inlineStr">
         <is>
           <t>76d4a800-1555-4b0e-a6b7-bdcb47516018</t>
@@ -9084,6 +9479,11 @@
           <t>hmmhmLLmM</t>
         </is>
       </c>
+      <c r="Q182" t="inlineStr">
+        <is>
+          <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
+        </is>
+      </c>
       <c r="R182" t="inlineStr">
         <is>
           <t>d3e32834-6f80-4957-ac5b-a1be0e260a44</t>
@@ -9116,6 +9516,11 @@
           <t>hmmhmLLmh</t>
         </is>
       </c>
+      <c r="Q183" t="inlineStr">
+        <is>
+          <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
+        </is>
+      </c>
       <c r="R183" t="inlineStr">
         <is>
           <t>3de5ed24-6134-418b-ba3e-f25a1039677a</t>
@@ -9146,6 +9551,11 @@
       <c r="K184" t="inlineStr">
         <is>
           <t>hmmhmLLlthrow</t>
+        </is>
+      </c>
+      <c r="Q184" t="inlineStr">
+        <is>
+          <t>9aa5afc6-6646-4750-b84c-b3114de16321</t>
         </is>
       </c>
       <c r="R184" t="inlineStr">

--- a/sources/king_step6b.xlsx
+++ b/sources/king_step6b.xlsx
@@ -1349,6 +1349,11 @@
           <t>– 1,2,1,2,1</t>
         </is>
       </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1,2,1,1,2</t>
+        </is>
+      </c>
       <c r="C19" t="inlineStr">
         <is>
           <t>– Ultimate Punches</t>
@@ -1396,6 +1401,11 @@
           <t>– 2,1,2,1,2</t>
         </is>
       </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>2,1,2,2,1</t>
+        </is>
+      </c>
       <c r="C20" t="inlineStr">
         <is>
           <t>– Ultimate Punches</t>
@@ -1441,6 +1451,11 @@
       <c r="A21" t="inlineStr">
         <is>
           <t>– 1,2,1</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>2,1,2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
